--- a/data/templates/teacher_template.xlsx
+++ b/data/templates/teacher_template.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xy/黎明教育/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\黎明教育\liming-course-system\data\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99464429-5133-044D-9DA3-54719A4F69E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945FE146-6EF1-4C9A-B6FD-EB6B2BAE9DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14460" yWindow="660" windowWidth="14180" windowHeight="15560" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="728" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="普通教师" sheetId="7" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">普通教师!$A$1:$B$68</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,22 +24,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>填写须知：
-1. 请勿修改表格结构
-2. 红色字段为必填项，黑色字段为选填项
-3. 教师姓名：必填，请使用教师真实姓名
-4. 手机号：必填，在本校内不可重复</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>教师姓名</t>
   </si>
@@ -50,61 +42,37 @@
     <t>手机号</t>
   </si>
   <si>
-    <t>何宇宗</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴泽宇</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>张扬升</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>李季</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>王悦烁</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>宋心葳</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>王自豪</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>晏杰英</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>陆诚俊</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>周杨洋</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <t>张君扬</t>
+  </si>
+  <si>
+    <t>李骥</t>
+  </si>
+  <si>
+    <t>王硕</t>
+  </si>
+  <si>
+    <t>晏英杰</t>
+  </si>
+  <si>
+    <t>陆俊诚</t>
+  </si>
+  <si>
+    <t>周奇洋</t>
+  </si>
+  <si>
+    <t>何君</t>
+  </si>
+  <si>
+    <t>吴昌泽</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -187,21 +155,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -239,52 +198,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,26 +516,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:N67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6328125" style="1" customWidth="1"/>
     <col min="3" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="126" customHeight="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:14" ht="17.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-    </row>
-    <row r="2" spans="1:14" ht="17">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <v>15922327108</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -597,328 +564,296 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="13" t="s">
-        <v>11</v>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="5">
-        <v>18098900798</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>19717786080</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>19533486330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
+        <v>19201870252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4">
-        <v>15922327108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="14" t="s">
+      <c r="B5" s="5">
+        <v>15225311072</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="5">
-        <v>19533486330</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="14" t="s">
+        <v>18098900798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5">
-        <v>19201870252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="13" t="s">
+        <v>19717786080</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="5">
-        <v>18395561219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="13" t="s">
+        <v>18851722750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="5">
-        <v>15249872935</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="B9" s="4">
         <v>15861667219</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="5">
-        <v>18851722750</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5">
-        <v>15225311072</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="7"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="6"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="7"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-    </row>
-    <row r="27" spans="1:2">
+      <c r="B26" s="7"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="7"/>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-    </row>
-    <row r="30" spans="1:2">
+      <c r="B29" s="7"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="7"/>
-    </row>
-    <row r="31" spans="1:2">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-    </row>
-    <row r="36" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-    </row>
-    <row r="42" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="8"/>
+      <c r="B41" s="9"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-    </row>
-    <row r="49" spans="1:2">
+      <c r="B48" s="8"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-    </row>
-    <row r="50" spans="1:2">
+      <c r="B49" s="9"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-    </row>
-    <row r="51" spans="1:2">
+      <c r="B50" s="8"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-    </row>
-    <row r="52" spans="1:2">
+      <c r="B51" s="9"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
       <c r="B52" s="9"/>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-    </row>
-    <row r="54" spans="1:2">
+      <c r="B53" s="8"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-    </row>
-    <row r="55" spans="1:2">
+      <c r="B54" s="9"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-    </row>
-    <row r="56" spans="1:2">
+      <c r="B55" s="8"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-    </row>
-    <row r="57" spans="1:2">
+      <c r="B56" s="9"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
       <c r="B57" s="9"/>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-    </row>
-    <row r="59" spans="1:2">
+      <c r="B58" s="8"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-    </row>
-    <row r="60" spans="1:2">
+      <c r="B59" s="9"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="8"/>
       <c r="B60" s="9"/>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="8"/>
       <c r="B61" s="9"/>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>
       <c r="B62" s="9"/>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>
       <c r="B64" s="9"/>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="8"/>
       <c r="B65" s="9"/>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="8"/>
       <c r="B66" s="9"/>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
+      <c r="B67" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B68" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
